--- a/Assets/StreamingAssets/Experiments.xlsx
+++ b/Assets/StreamingAssets/Experiments.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -463,6 +463,8 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -518,30 +520,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SpeedLimitKmh</t>
+          <t>RebelShare</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>StreetSpeedLimitKmh</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>AvenueSpeedLimitKmh</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>GreenLightSeconds</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>DurationMinutes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>WarmupMinutes</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>FirstSeed</t>
         </is>
@@ -583,21 +595,27 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>30</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
+        <v>50</v>
+      </c>
+      <c r="N2" t="n">
         <v>15</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>20</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -747,7 +765,7 @@
           <t>Traffic lights change every 8 s instead of 15 s.</t>
         </is>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -762,23 +780,86 @@
           <t>Traffic lights change every 30 s.</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SpeedLimit50</t>
+          <t>SlowAvenues</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Speed limit 50 km/h instead of 30.</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>50</v>
+          <t>Avenues limited to 30 km/h like every other street.</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Rebels10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1 in 10 ambient drivers ignores every traffic rule.</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Rebels25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1 in 4 ambient drivers ignores every traffic rule.</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Rebels50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Half the ambient drivers ignore every traffic rule.</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Rebels25DoubleFleet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1 in 4 rebels, with twice as many taxis.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -915,105 +996,129 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Each ambient driver gets a random calmness between these (0 = in a hurry, 1 = very calm; default 0 and 1).</t>
+          <t>Each law-abiding driver gets a random calmness between these (0 = in a hurry, 1 = very calm; default 0 and 1).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SpeedLimitKmh</t>
+          <t>RebelShare</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Speed limit of every street (default 30).</t>
+          <t>Share of ambient drivers (0 to 1) who ignore every traffic rule: they run red lights, speed (60 km/h), don't give way and can crash. Taxis always follow the rules (default 0).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>GreenLightSeconds</t>
+          <t>StreetSpeedLimitKmh</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>How long each direction of an intersection stays green (default 15; then 3 s yellow and 2 s all red).</t>
+          <t>Speed limit of one-lane streets and of the roundabout (default 30).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>DurationMinutes</t>
+          <t>AvenueSpeedLimitKmh</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Simulated minutes per run (default 20).</t>
+          <t>Speed limit of avenues, streets with two lanes side by side (default 50).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>WarmupMinutes</t>
+          <t>GreenLightSeconds</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>The first minutes are left out of the summary while the city fills up (default 2).</t>
+          <t>How long each direction of an intersection stays green (default 15; then 3 s yellow and 2 s all red).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>DurationMinutes</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>How many runs, each with different random choices (default 5). More seeds = more reliable averages.</t>
+          <t>Simulated minutes per run (default 20).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>WarmupMinutes</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>The first minutes are left out of the summary while the city fills up (default 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Seeds</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>How many runs, each with different random choices (default 5). More seeds = more reliable averages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>FirstSeed</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Seeds used are FirstSeed, FirstSeed+1, ... (default 1). Same seed = same run.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>How to run</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Unity: Traffic Simulation &gt; Experiments. Terminal: Unity -batchmode -quit -projectPath . -executeMethod ExperimentsCommandLine.RunAll -excelReport</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>ExperimentResults/&lt;date&gt;/ next to Assets: CSV files, plus report.xlsx and charts after the Excel report.</t>
         </is>
